--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512452_1ºDA1ºDBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512452_1ºDA1ºDBFINAL_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0845</v>
+        <v>3.9124</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9174</v>
+        <v>3.4213</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8329</v>
+        <v>0.491</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.225</v>
+        <v>2.614</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5537</v>
+        <v>0.3058</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3287</v>
+        <v>2.3082</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3128</v>
+        <v>2.0165</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4526</v>
+        <v>0.0873</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7655</v>
+        <v>1.9292</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5378</v>
+        <v>0.5975</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.101</v>
+        <v>0.2185</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4367</v>
+        <v>0.379</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3691</v>
+        <v>0.9405</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7451</v>
+        <v>0.2354</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.376</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1398</v>
+        <v>-1.3947</v>
       </c>
       <c r="W2" t="n">
-        <v>2.0594</v>
+        <v>1.1695</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9196</v>
+        <v>-2.5642</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0773</v>
+        <v>2.8242</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6714</v>
+        <v>4.7282</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4059</v>
+        <v>-1.904</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6315</v>
+        <v>-0.1885</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3225</v>
+        <v>-0.5306</v>
       </c>
       <c r="I3" t="n">
-        <v>2.309</v>
+        <v>0.3421</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9052</v>
+        <v>1.5179</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0236</v>
+        <v>-0.3385</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8816</v>
+        <v>1.8565</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7262</v>
+        <v>-1.7064</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2989</v>
+        <v>-0.192</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4274</v>
+        <v>-1.5144</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8005</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0454</v>
+        <v>1.1027</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3533</v>
+        <v>1.294</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3987</v>
+        <v>-0.1913</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4001</v>
+        <v>0.1574</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1195</v>
+        <v>2.1111</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.5195</v>
+        <v>-1.9537</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0071</v>
+        <v>1.711</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6432</v>
+        <v>0.5625</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6361</v>
+        <v>1.1485</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7793</v>
+        <v>-0.4355</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1043</v>
+        <v>-0.6948</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8837</v>
+        <v>0.2592</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4435</v>
+        <v>-0.6106</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2835</v>
+        <v>-0.6106</v>
       </c>
       <c r="L4" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2229</v>
+        <v>0.1751</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1792</v>
+        <v>-0.0842</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0437</v>
+        <v>0.2592</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2006</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6005</v>
+        <v>0.3895</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8467</v>
+        <v>-0.1777</v>
       </c>
       <c r="T4" t="n">
-        <v>2.681</v>
+        <v>-0.048</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1657</v>
+        <v>-0.1297</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4601</v>
+        <v>1.9347</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7194</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.1794</v>
+        <v>0.7137</v>
       </c>
     </row>
     <row r="5">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4997</v>
+        <v>1.5316</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4997</v>
+        <v>1.5316</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4997</v>
+        <v>1.5316</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9237</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4997</v>
+        <v>1.5316</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9237</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4855</v>
+        <v>0.6909</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2857</v>
+        <v>1.0353</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1998</v>
+        <v>-0.3444</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4356</v>
+        <v>0.5208</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7136</v>
+        <v>0.1221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2781</v>
+        <v>0.3987</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6562</v>
+        <v>0.0616</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6562</v>
+        <v>0.0616</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2206</v>
+        <v>0.4592</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0574</v>
+        <v>0.0605</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2781</v>
+        <v>0.3987</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4001</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4393</v>
+        <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2578</v>
+        <v>-0.2473</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1814</v>
+        <v>0.4174</v>
       </c>
       <c r="V6" t="n">
-        <v>1.9603</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7605</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6863</v>
+        <v>0.3951</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0019</v>
+        <v>1.7241</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3156</v>
+        <v>-1.3289</v>
       </c>
       <c r="G7" t="n">
-        <v>0.538</v>
+        <v>-0.827</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1312</v>
+        <v>0.1134</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4068</v>
+        <v>-0.9405</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06</v>
+        <v>0.5163</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06</v>
+        <v>0.3542</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1621</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4781</v>
+        <v>-1.3433</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0713</v>
+        <v>-0.2407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4068</v>
+        <v>-1.1026</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1483</v>
+        <v>2.2595</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2578</v>
+        <v>1.5699</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4061</v>
+        <v>0.6896</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.4532</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.78</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1998</v>
+        <v>-2.2332</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.257</v>
+        <v>0.1782</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8773</v>
+        <v>-2.2658</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6203</v>
+        <v>2.444</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5981</v>
+        <v>-0.5777</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1687</v>
+        <v>0.1858</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7667</v>
+        <v>-0.7634</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6323</v>
+        <v>-1.5501</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3163</v>
+        <v>-0.2616</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.316</v>
+        <v>-1.2885</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0342</v>
+        <v>0.9725</v>
       </c>
       <c r="N8" t="n">
-        <v>0.485</v>
+        <v>0.4474</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5493</v>
+        <v>0.525</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0587</v>
+        <v>0.3401</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6446</v>
+        <v>-0.1578</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5858</v>
+        <v>0.4979</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5255</v>
+        <v>-0.6479</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5236</v>
+        <v>-1.2234</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9981</v>
+        <v>0.5756</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5151</v>
+        <v>-0.5442</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4465</v>
+        <v>1.4661</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9616</v>
+        <v>-2.0102</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2345</v>
+        <v>-0.1483</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2835</v>
+        <v>0.3542</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.518</v>
+        <v>-0.5024</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2806</v>
+        <v>-0.3959</v>
       </c>
       <c r="N9" t="n">
-        <v>1.163</v>
+        <v>1.1119</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4436</v>
+        <v>-1.5078</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.091</v>
+        <v>-0.129</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2889</v>
+        <v>-0.1015</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1979</v>
+        <v>-0.0275</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7231</v>
+        <v>-1.2081</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0026</v>
+        <v>-3.6141</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2795</v>
+        <v>2.4059</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3755</v>
+        <v>-1.3866</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7493</v>
+        <v>-0.725</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6262</v>
+        <v>-0.6615</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4303</v>
+        <v>-2.3394</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9122</v>
+        <v>-1.837</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.518</v>
+        <v>-0.5024</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0548</v>
+        <v>0.9528</v>
       </c>
       <c r="N10" t="n">
-        <v>1.163</v>
+        <v>1.1119</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0067</v>
+        <v>0.4305</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.031</v>
+        <v>0.1458</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0243</v>
+        <v>0.2847</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5468</v>
+        <v>-4.1445</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1099</v>
+        <v>-2.4213</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4369</v>
+        <v>-1.7232</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0179</v>
+        <v>1.0108</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5468</v>
+        <v>0.5424</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4712</v>
+        <v>0.4684</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0269</v>
+        <v>3.183</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5834</v>
+        <v>0.662</v>
       </c>
       <c r="L11" t="n">
-        <v>2.4435</v>
+        <v>2.521</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.009</v>
+        <v>-2.1722</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0367</v>
+        <v>-0.1197</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9723</v>
+        <v>-2.0526</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.2012</v>
+        <v>-4.0895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.2018</v>
+        <v>-6.0368</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5561</v>
+        <v>0.8879</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7451</v>
+        <v>1.0946</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1891</v>
+        <v>-0.2068</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.9196</v>
+        <v>-1.9537</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2394</v>
+        <v>-1.2916</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.8364</v>
+        <v>-5.7476</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.8204</v>
+        <v>-6.2117</v>
       </c>
       <c r="F12" t="n">
-        <v>0.984</v>
+        <v>0.4642</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.7926</v>
+        <v>-6.7113</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.316</v>
+        <v>-1.288</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.4766</v>
+        <v>-5.4233</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.4546</v>
+        <v>-6.2259</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7505</v>
+        <v>-1.6394</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.7041</v>
+        <v>-4.5866</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.338</v>
+        <v>-0.4854</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4345</v>
+        <v>0.3514</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7725</v>
+        <v>-0.8368</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7238</v>
+        <v>0.2806</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2247</v>
+        <v>0.0452</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5008</v>
+        <v>0.2353</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4799</v>
+        <v>0.4884</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5795</v>
+        <v>-1.6226</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.048400000000001</v>
+        <v>-0.5047000000000024</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.314499999999999</v>
+        <v>-2.733300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2661</v>
+        <v>2.2287</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.0341</v>
+        <v>-4.9936</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2871000000000001</v>
+        <v>0.4209000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.3211</v>
+        <v>-5.414400000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1598</v>
+        <v>-2.047400000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.9541</v>
+        <v>-2.2441</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2056000000000004</v>
+        <v>0.1968000000000005</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8744</v>
+        <v>-2.946099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2414</v>
+        <v>2.665</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.1154</v>
+        <v>-5.6114</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.0046</v>
+        <v>-15.5788</v>
       </c>
       <c r="R13" t="n">
-        <v>14.0041</v>
+        <v>13.6316</v>
       </c>
       <c r="S13" t="n">
-        <v>5.6461</v>
+        <v>6.1051</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1131</v>
+        <v>3.8303</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5328</v>
+        <v>2.2747</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3401000000000001</v>
+        <v>0.3309</v>
       </c>
       <c r="W13" t="n">
-        <v>10.7366</v>
+        <v>11.0628</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.3963</v>
+        <v>-10.7317</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7866</v>
+        <v>4.8903</v>
       </c>
       <c r="E14" t="n">
-        <v>2.196</v>
+        <v>3.1811</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5906</v>
+        <v>1.7092</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7649</v>
+        <v>4.7504</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2052</v>
+        <v>2.1567</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5596</v>
+        <v>2.5937</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1467</v>
+        <v>4.3225</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6213</v>
+        <v>1.696</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5254</v>
+        <v>2.6265</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6182</v>
+        <v>0.4279</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5839</v>
+        <v>0.4607</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4456</v>
+        <v>-1.3895</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2691</v>
+        <v>-0.611</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1765</v>
+        <v>-0.7785</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6674</v>
+        <v>1.7241</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3192</v>
+        <v>2.3905</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6518</v>
+        <v>-0.6664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5816</v>
+        <v>2.125</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9191</v>
+        <v>1.4311</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6625</v>
+        <v>0.6939</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6693</v>
+        <v>0.1987</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4017</v>
+        <v>-0.9247</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0709</v>
+        <v>1.1234</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3636</v>
+        <v>0.0012</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-1.288</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9216</v>
+        <v>1.2891</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3057</v>
+        <v>0.1975</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1563</v>
+        <v>0.3632</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1493</v>
+        <v>-0.1657</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5684</v>
+        <v>-1.4072</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4445</v>
+        <v>-0.6811</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1239</v>
+        <v>-0.7261</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3197</v>
+        <v>1.7757</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.1111</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.3197</v>
+        <v>-0.3354</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4347</v>
+        <v>1.7669</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9244</v>
+        <v>1.3038</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5103</v>
+        <v>0.4631</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2158</v>
+        <v>1.6456</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8885</v>
+        <v>-0.4439</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1042</v>
+        <v>2.0895</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1105</v>
+        <v>1.4284</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.316</v>
+        <v>-0.5413</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2055</v>
+        <v>1.9697</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3262</v>
+        <v>0.2172</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4275</v>
+        <v>0.0974</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1013</v>
+        <v>0.1198</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6005</v>
+        <v>1.7526</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1292</v>
+        <v>-0.2882</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0246</v>
+        <v>-0.1246</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1046</v>
+        <v>-0.1636</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7477</v>
+        <v>-1.3432</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0594</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3117</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0776</v>
+        <v>0.7957</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3285</v>
+        <v>-1.3162</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.251</v>
+        <v>2.1119</v>
       </c>
       <c r="G17" t="n">
-        <v>1.126</v>
+        <v>0.9746</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6198</v>
+        <v>0.1093</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5062</v>
+        <v>0.8653</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4709</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1854</v>
+        <v>-0.254</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2855</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3449</v>
+        <v>0.337</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4345</v>
+        <v>0.3632</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7793</v>
+        <v>-0.0262</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4004</v>
+        <v>0.1947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0003</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4007</v>
+        <v>2.1421</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6909</v>
+        <v>0.0279</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3383</v>
+        <v>-0.0064</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6475</v>
+        <v>0.0344</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.1398</v>
+        <v>-0.4016</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6593</v>
+        <v>-0.4016</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0563</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8299</v>
+        <v>-1.8065</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8862</v>
+        <v>2.3201</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0567</v>
+        <v>0.4467</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1494</v>
+        <v>1.6929</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9073</v>
+        <v>-1.2462</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6018</v>
+        <v>-0.3982</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2781</v>
+        <v>0.9546</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8799</v>
+        <v>-1.3528</v>
       </c>
       <c r="M18" t="n">
-        <v>0.455</v>
+        <v>0.8449</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4275</v>
+        <v>0.7383</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0274</v>
+        <v>0.1067</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2006</v>
+        <v>2.3368</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1793</v>
+        <v>-1.6615</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4311</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6104000000000001</v>
+        <v>-0.9795</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3798</v>
+        <v>1.3388</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3798</v>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0799</v>
+        <v>-0.11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2254</v>
+        <v>1.5754</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3054</v>
+        <v>-1.6854</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0441</v>
+        <v>1.1763</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1418</v>
+        <v>0.6363</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9023</v>
+        <v>0.54</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6141</v>
+        <v>1.6551</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2981</v>
+        <v>0.2849</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.316</v>
+        <v>1.3702</v>
       </c>
       <c r="M19" t="n">
-        <v>0.57</v>
+        <v>-0.4788</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1563</v>
+        <v>0.3514</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4137</v>
+        <v>-0.8302</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6002</v>
+        <v>1.3632</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6002</v>
+        <v>2.3368</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7561</v>
+        <v>-0.4868</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4603</v>
+        <v>0.335</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2958</v>
+        <v>-0.8219</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3921</v>
+        <v>-2.1626</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3793</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7713</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5411</v>
+        <v>-0.7426</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8024</v>
+        <v>-0.3392</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2613</v>
+        <v>-0.4033</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3498</v>
+        <v>-1.0734</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6552</v>
+        <v>-0.1771</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3053</v>
+        <v>-0.8963</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6614</v>
+        <v>-1.563</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.2745</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4684</v>
+        <v>-1.2885</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0112</v>
+        <v>0.4896</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8482</v>
+        <v>0.0974</v>
       </c>
       <c r="O20" t="n">
-        <v>0.163</v>
+        <v>0.3921</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4007</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6392</v>
+        <v>0.1336</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3402</v>
+        <v>-0.2252</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.299</v>
+        <v>0.3588</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3481</v>
+        <v>-0.3869</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1998</v>
+        <v>1.449</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1483</v>
+        <v>-1.8359</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0341</v>
+        <v>-1.502</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0757</v>
+        <v>-0.9473</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0416</v>
+        <v>-0.5548</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8155</v>
+        <v>-0.8213</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9092</v>
+        <v>-0.8893</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0679</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9925</v>
+        <v>-0.8938</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0725</v>
+        <v>-0.9749</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.177</v>
+        <v>0.0725</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1633</v>
+        <v>0.0856</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2263</v>
+        <v>-0.7148</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4822</v>
+        <v>-0.5482</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2559</v>
+        <v>-0.1666</v>
       </c>
       <c r="V21" t="n">
-        <v>1.008</v>
+        <v>1.0078</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3915</v>
+        <v>-1.4343</v>
       </c>
     </row>
     <row r="22">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7469</v>
+        <v>-1.7515</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2378</v>
+        <v>-0.2268</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5091</v>
+        <v>-1.5247</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.173</v>
+        <v>-0.1966</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3086</v>
+        <v>-0.3295</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.02</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.193</v>
+        <v>-0.2171</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3286</v>
+        <v>-0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,22 +2170,22 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3741</v>
+        <v>-0.3339</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2578</v>
+        <v>-0.2473</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1163</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4862</v>
+        <v>-4.8623</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9136</v>
+        <v>-5.084</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4274</v>
+        <v>0.2217</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1158</v>
+        <v>-2.1074</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.267</v>
+        <v>-2.2517</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1512</v>
+        <v>0.1442</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3502</v>
+        <v>-2.2641</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.3521</v>
+        <v>-2.2886</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0019</v>
+        <v>0.0244</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2344</v>
+        <v>0.1567</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0851</v>
+        <v>0.0369</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.8008</v>
+        <v>-2.7263</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1106</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9182</v>
+        <v>0.5159</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1924</v>
+        <v>0.1177</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0486</v>
+        <v>1.123099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.265999999999999</v>
+        <v>-2.228599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>5.314399999999999</v>
+        <v>3.3517</v>
       </c>
       <c r="G24" t="n">
-        <v>5.0341</v>
+        <v>4.9936</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2871999999999997</v>
+        <v>-0.4210000000000003</v>
       </c>
       <c r="I24" t="n">
-        <v>5.3211</v>
+        <v>5.414400000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>1.874299999999999</v>
+        <v>2.9462</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.2411</v>
+        <v>-2.6653</v>
       </c>
       <c r="L24" t="n">
-        <v>5.1154</v>
+        <v>5.6113</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1598</v>
+        <v>2.0474</v>
       </c>
       <c r="N24" t="n">
-        <v>2.954</v>
+        <v>2.2441</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2056999999999999</v>
+        <v>-0.1967</v>
       </c>
       <c r="P24" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q24" t="n">
-        <v>-14.0041</v>
+        <v>-13.6316</v>
       </c>
       <c r="R24" t="n">
-        <v>16.0046</v>
+        <v>15.5788</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.645900000000001</v>
+        <v>-5.4868</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.5327</v>
+        <v>-2.2749</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.1133</v>
+        <v>-3.2118</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3402000000000002</v>
+        <v>-0.3310999999999998</v>
       </c>
       <c r="W24" t="n">
-        <v>10.3964</v>
+        <v>10.7318</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.7364</v>
+        <v>-11.0628</v>
       </c>
     </row>
   </sheetData>
